--- a/251211/NMDAR_Coma.xlsx
+++ b/251211/NMDAR_Coma.xlsx
@@ -383,11 +383,11 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9959</v>
+        <v>0.9601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9701 – 1.0216</t>
+          <t>0.7379 – 1.2379</t>
         </is>
       </c>
       <c r="D2">
@@ -401,11 +401,11 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.0009</v>
+        <v>1.0095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9766 – 1.0249</t>
+          <t>0.7895 – 1.2785</t>
         </is>
       </c>
       <c r="D3">
@@ -419,11 +419,11 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9867</v>
+        <v>0.8744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9625 – 1.0097</t>
+          <t>0.6822 – 1.1016</t>
         </is>
       </c>
       <c r="D4">
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.0041</v>
+        <v>1.0413</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9824 – 1.0256</t>
+          <t>0.837 – 1.2872</t>
         </is>
       </c>
       <c r="D5">
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.5473</v>
+        <v>0.9415</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0554 – 4.4428</t>
+          <t>0.7488 – 1.1608</t>
         </is>
       </c>
       <c r="D6">
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.537</v>
+        <v>0.9397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0637 – 3.543</t>
+          <t>0.7593 – 1.1348</t>
         </is>
       </c>
       <c r="D7">
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.5152</v>
+        <v>0.9358</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0689 – 3.2097</t>
+          <t>0.7653 – 1.1237</t>
         </is>
       </c>
       <c r="D8">
@@ -509,11 +509,11 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.7612</v>
+        <v>0.9731</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.1147 – 4.325</t>
+          <t>0.8053 – 1.1577</t>
         </is>
       </c>
       <c r="D9">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9933999999999999</v>
+        <v>0.9356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9637 – 1.0219</t>
+          <t>0.6907 – 1.2416</t>
         </is>
       </c>
       <c r="D10">
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9986</v>
+        <v>0.9858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9711 – 1.025</t>
+          <t>0.7459 – 1.2804</t>
         </is>
       </c>
       <c r="D11">
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.9822</v>
+        <v>0.8354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9535 – 1.0091</t>
+          <t>0.6209 – 1.095</t>
         </is>
       </c>
       <c r="D12">
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.0009</v>
+        <v>1.0087</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9756 – 1.0252</t>
+          <t>0.7808 – 1.2828</t>
         </is>
       </c>
       <c r="D13">
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.0023</v>
+        <v>1.0228</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9811 – 1.0229</t>
+          <t>0.8261 – 1.2537</t>
         </is>
       </c>
       <c r="D14">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.9946</v>
+        <v>0.9474</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.971 – 1.0179</t>
+          <t>0.7453 – 1.1942</t>
         </is>
       </c>
       <c r="D15">
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.9928</v>
+        <v>0.9307</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9707 – 1.0144</t>
+          <t>0.7425 – 1.1533</t>
         </is>
       </c>
       <c r="D16">
@@ -653,11 +653,11 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9906</v>
+        <v>0.9102</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9682 – 1.0121</t>
+          <t>0.7239 – 1.128</t>
         </is>
       </c>
       <c r="D17">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.9973</v>
+        <v>0.9737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9752 – 1.019</t>
+          <t>0.7777 – 1.2076</t>
         </is>
       </c>
       <c r="D18">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.0008</v>
+        <v>1.0082</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9801 – 1.0209</t>
+          <t>0.8181 – 1.2293</t>
         </is>
       </c>
       <c r="D19">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.9859</v>
+        <v>0.8679</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9642 – 1.0064</t>
+          <t>0.6948 – 1.0661</t>
         </is>
       </c>
       <c r="D20">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.0029</v>
+        <v>1.0292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.9839 – 1.0215</t>
+          <t>0.8498 – 1.2376</t>
         </is>
       </c>
       <c r="D21">
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.9923</v>
+        <v>0.926</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.9598 – 1.0243</t>
+          <t>0.6633 – 1.2711</t>
         </is>
       </c>
       <c r="D22">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.9988</v>
+        <v>0.9879</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.9686 – 1.0284</t>
+          <t>0.7269 – 1.3232</t>
         </is>
       </c>
       <c r="D23">
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.9875</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.9582 – 1.0152</t>
+          <t>0.6528 – 1.1623</t>
         </is>
       </c>
       <c r="D24">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.006</v>
+        <v>1.0617</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9797 – 1.0318</t>
+          <t>0.8145 – 1.3682</t>
         </is>
       </c>
       <c r="D25">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.9981</v>
+        <v>0.9807</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.976 – 1.0197</t>
+          <t>0.7841 – 1.2151</t>
         </is>
       </c>
       <c r="D26">
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.0009</v>
+        <v>1.0087</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.9802 – 1.0208</t>
+          <t>0.8191 – 1.2291</t>
         </is>
       </c>
       <c r="D27">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.9861</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.9645 – 1.0065</t>
+          <t>0.6966 – 1.0671</t>
         </is>
       </c>
       <c r="D28">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.003</v>
+        <v>1.0305</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.984 – 1.0216</t>
+          <t>0.8511 – 1.2389</t>
         </is>
       </c>
       <c r="D29">
